--- a/Electronic Invite Excel Template (Blank).xlsx
+++ b/Electronic Invite Excel Template (Blank).xlsx
@@ -802,16 +802,16 @@
       <formula1>Dropdown!$E$2:$E$61</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2" type="date">
-      <formula1>Dropdown!G2</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:M2" type="list">
+      <formula1>Dropdown!$H$2:$H$42</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C2" type="date">
-      <formula1>Dropdown!G2</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C2" type="date">
+      <formula1>Dropdown!F2</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:M2" type="list">
-      <formula1>Dropdown!$H$2:$H$42</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2" type="date">
+      <formula1>Dropdown!G2</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -881,7 +881,7 @@
       </c>
       <c r="F2" s="8" t="n">
         <f aca="true">TODAY()</f>
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="G2" s="8" t="n">
         <v>64651</v>
